--- a/downloads/en/secteurs-revues.xlsx
+++ b/downloads/en/secteurs-revues.xlsx
@@ -460,7 +460,7 @@
         <v>181</v>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
